--- a/site/Dayforce-Entra-ID-Writeback-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Entra-ID-Writeback-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Entra application</t>
+          <t>Entra ID application</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Rules</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -881,51 +881,51 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Debug Filter - Writeback</t>
+          <t>Operational Settings</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KSEZ1N41WY3X8THTWYC1NQ3Q</t>
+          <t>h_01KN47NYDZ014D07BNJKKQFDED</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01KSEZ1N41WY3X8THTWYC1NQ3Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01KN47NYDZ014D07BNJKKQFDED</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Operational Settings</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KN47NYDZ014D07BNJKKQFDED</t>
+          <t>h_01KSHXF7YZXW8XYHPBW0GGX85G</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01KN47NYDZ014D07BNJKKQFDED</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01KSHXF7YZXW8XYHPBW0GGX85G</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Logging Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KSHXF7YZXW8XYHPBW0GGX85G</t>
+          <t>h_01KSHXF7Z06V0RVBS9CW6CEYFP</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01KSHXF7YZXW8XYHPBW0GGX85G</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01KSHXF7Z06V0RVBS9CW6CEYFP</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,63 +957,63 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KSHXF7Z06V0RVBS9CW6CEYFP</t>
+          <t>h_01KSHXF7Z0MW8W49X4TTD453F9</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01KSHXF7Z06V0RVBS9CW6CEYFP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01KSHXF7Z0MW8W49X4TTD453F9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KSHXF7Z0MW8W49X4TTD453F9</t>
+          <t>h_01KSEWDZWGHZ8G8RDA1E958XZK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01KSHXF7Z0MW8W49X4TTD453F9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01KSEWDZWGHZ8G8RDA1E958XZK</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Channels</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KSEWDZWGHZ8G8RDA1E958XZK</t>
+          <t>h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01KSEWDZWGHZ8G8RDA1E958XZK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Channels</t>
+          <t>Template Library</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
+          <t>h_01KN1AVFK47V9644J22EQEDVZE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01KN1AVFK47V9644J22EQEDVZE</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Template Library</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,63 +1045,63 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KN1AVFK47V9644J22EQEDVZE</t>
+          <t>h_01KN1AVMW81679JNM3NZGGKJAY</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01KN1AVFK47V9644J22EQEDVZE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01KN1AVMW81679JNM3NZGGKJAY</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KN1AVMW81679JNM3NZGGKJAY</t>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01KN1AVMW81679JNM3NZGGKJAY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1111,32 +1111,10 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Entra-ID-Writeback-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
